--- a/Input/Tiendas_No generar pedido.xlsx
+++ b/Input/Tiendas_No generar pedido.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prestamo\Documents\Isimo\Proyectos\Distribucion de Fruver\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B80EF1-9E5E-4D90-9BE5-09B6A6EC3890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7825B37-4420-44FA-8336-EF6A1F436F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Input/Tiendas_No generar pedido.xlsx
+++ b/Input/Tiendas_No generar pedido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prestamo\Documents\Isimo\Proyectos\Distribucion de Fruver\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7825B37-4420-44FA-8336-EF6A1F436F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44035C6E-9F9E-4C52-93AC-EB439C937C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Centro Operacional de la Bodega</t>
   </si>
@@ -45,6 +45,33 @@
   </si>
   <si>
     <t>ISIMO TO GO</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>S70</t>
+  </si>
+  <si>
+    <t>S83</t>
+  </si>
+  <si>
+    <t>SA5</t>
+  </si>
+  <si>
+    <t>SE8</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>SA6</t>
   </si>
 </sst>
 </file>
@@ -413,7 +440,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.5703125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
@@ -433,17 +460,50 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="B3" s="2"/>
     </row>
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Input/Tiendas_No generar pedido.xlsx
+++ b/Input/Tiendas_No generar pedido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prestamo\Documents\Isimo\Proyectos\Distribucion de Fruver\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44035C6E-9F9E-4C52-93AC-EB439C937C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FF7206-EB2E-423F-AAC7-634E64AF7945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Centro Operacional de la Bodega</t>
   </si>
@@ -45,33 +45,6 @@
   </si>
   <si>
     <t>ISIMO TO GO</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>S34</t>
-  </si>
-  <si>
-    <t>S70</t>
-  </si>
-  <si>
-    <t>S83</t>
-  </si>
-  <si>
-    <t>SA5</t>
-  </si>
-  <si>
-    <t>SE8</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>SA6</t>
   </si>
 </sst>
 </file>
@@ -440,7 +413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.5703125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
@@ -460,50 +433,17 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="A3" s="1"/>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-    </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
+      <c r="A7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Input/Tiendas_No generar pedido.xlsx
+++ b/Input/Tiendas_No generar pedido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prestamo\Documents\Isimo\Proyectos\Distribucion de Fruver\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FF7206-EB2E-423F-AAC7-634E64AF7945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A53786-7FE7-44E5-B8FA-02C029CE25BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Centro Operacional de la Bodega</t>
   </si>
@@ -45,6 +45,120 @@
   </si>
   <si>
     <t>ISIMO TO GO</t>
+  </si>
+  <si>
+    <t>SD8</t>
+  </si>
+  <si>
+    <t>COSTA AZUL</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>NORMANDIA OCCIDENTAL 2</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>FACA SANTANDER</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>FUNZA ZUAME</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>CHIPAQUE CENTRO</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>FUSAGASUGA</t>
+  </si>
+  <si>
+    <t>S70</t>
+  </si>
+  <si>
+    <t>SILVANIA</t>
+  </si>
+  <si>
+    <t>SA4</t>
+  </si>
+  <si>
+    <t>ISIMO LOMAS</t>
+  </si>
+  <si>
+    <t>SA5</t>
+  </si>
+  <si>
+    <t>ISIMO EL TRÉBOL</t>
+  </si>
+  <si>
+    <t>SA6</t>
+  </si>
+  <si>
+    <t>ISIMO VARIANTE CELTA</t>
+  </si>
+  <si>
+    <t>SB3</t>
+  </si>
+  <si>
+    <t>ISIMO LA ESTACIÓN</t>
+  </si>
+  <si>
+    <t>SB8</t>
+  </si>
+  <si>
+    <t>ISIMO MONTANA</t>
+  </si>
+  <si>
+    <t>SC0</t>
+  </si>
+  <si>
+    <t>ISIMO DIVINO NIÑO</t>
+  </si>
+  <si>
+    <t>SC2</t>
+  </si>
+  <si>
+    <t>ISIMO VILLA SUAITA</t>
+  </si>
+  <si>
+    <t>SC4</t>
+  </si>
+  <si>
+    <t>ISIMO BRAVO PÁEZ</t>
+  </si>
+  <si>
+    <t>SD3</t>
+  </si>
+  <si>
+    <t>ISIMO TINTALITO</t>
+  </si>
+  <si>
+    <t>SD4</t>
+  </si>
+  <si>
+    <t>ISIMO LOS LIBERTADORES</t>
+  </si>
+  <si>
+    <t>SE5</t>
+  </si>
+  <si>
+    <t>MOLINOS</t>
+  </si>
+  <si>
+    <t>SE8</t>
+  </si>
+  <si>
+    <t>FUSAGASUGA BALMORAL</t>
   </si>
 </sst>
 </file>
@@ -59,10 +173,9 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
       <sz val="8"/>
       <color indexed="8"/>
-      <name val="Verdana"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -88,7 +201,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -413,37 +526,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.5703125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.5703125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="13.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1"/>
+    <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
